--- a/sources/ogre_step8c.xlsx
+++ b/sources/ogre_step8c.xlsx
@@ -7503,12 +7503,12 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">

--- a/sources/ogre_step8c.xlsx
+++ b/sources/ogre_step8c.xlsx
@@ -857,6 +857,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>d39eb950-752d-4877-9aa7-36a04ab131b5</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>d39eb950-752d-4877-9aa7-36a04ab131b5</t>
@@ -919,6 +924,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>64b3364c-2ddc-4c41-a1df-c8c0c11f1274</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>64b3364c-2ddc-4c41-a1df-c8c0c11f1274</t>
@@ -979,6 +989,11 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>f9b36b8d-0849-48e2-82e6-616a4a498ad1</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">

--- a/sources/ogre_step8c.xlsx
+++ b/sources/ogre_step8c.xlsx
@@ -417,38 +417,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AD91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="85" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col hidden="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col hidden="1" min="10" max="10"/>
-    <col width="47" customWidth="1" min="11" max="11"/>
-    <col hidden="1" min="12" max="12"/>
-    <col width="37" customWidth="1" min="13" max="13"/>
-    <col hidden="1" min="14" max="14"/>
-    <col width="37" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col hidden="1" min="17" max="17"/>
-    <col width="37" customWidth="1" min="18" max="18"/>
-    <col hidden="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="115" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="38" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="85" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col hidden="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col hidden="1" min="11" max="11"/>
+    <col width="47" customWidth="1" min="12" max="12"/>
+    <col hidden="1" min="13" max="13"/>
+    <col width="37" customWidth="1" min="14" max="14"/>
+    <col hidden="1" min="15" max="15"/>
+    <col width="37" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col hidden="1" min="18" max="18"/>
+    <col width="37" customWidth="1" min="19" max="19"/>
+    <col hidden="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="115" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="38" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,125 +482,130 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -616,57 +622,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Body Slam</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Body Slam</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>a2f6aa83-0f3a-4958-afa1-02b9b273a1d4</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>90ba6eb3-fc65-4f2b-a4fb-244639b358d8</t>
         </is>
@@ -683,57 +689,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Bear Hug</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Bear Hug</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>3e81ad6e-c480-43ee-a702-e7db069d9511</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>63ecc894-cabb-4742-bf7d-cd465b2d4cd2</t>
         </is>
@@ -750,57 +756,57 @@
           <t>df,DF+2+4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Waning Moon</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Waning Moon</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>22cb5474-51db-4acf-b543-a752d6744b1a</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>02409448-cd27-4988-8d70-c230576d7f87</t>
         </is>
@@ -824,50 +830,55 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Choke Slam</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Choke Slam</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>10,15,25</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>10,15,25</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>d39eb950-752d-4877-9aa7-36a04ab131b5</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>d39eb950-752d-4877-9aa7-36a04ab131b5</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -891,50 +902,55 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Rag Doll</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Rag Doll</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>64b3364c-2ddc-4c41-a1df-c8c0c11f1274</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>64b3364c-2ddc-4c41-a1df-c8c0c11f1274</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -958,50 +974,55 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Bear Swing</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Bear Swing</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>f9b36b8d-0849-48e2-82e6-616a4a498ad1</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>f9b36b8d-0849-48e2-82e6-616a4a498ad1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1038,125 +1059,130 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
+      <c r="Q11" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="inlineStr">
+      <c r="R11" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R11" s="1" t="inlineStr">
+      <c r="S11" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S11" s="1" t="inlineStr">
+      <c r="T11" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T11" s="1" t="inlineStr">
+      <c r="U11" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U11" s="1" t="inlineStr">
+      <c r="V11" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V11" s="1" t="inlineStr">
+      <c r="W11" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
+      <c r="X11" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X11" s="1" t="inlineStr">
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y11" s="1" t="inlineStr">
+      <c r="Z11" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="AA11" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
+      <c r="AB11" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
+      <c r="AC11" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC11" s="1" t="inlineStr">
+      <c r="AD11" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1173,77 +1199,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>411575b7-89f6-4910-b889-87be425ae707</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>9b270e1c-2774-4e6b-8ddc-b52b8b714bfe</t>
         </is>
@@ -1260,77 +1286,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>61c76392-af9b-42cc-b100-c0721822c502</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>9416cfff-36b5-4a56-8c66-bd21c191a231</t>
         </is>
@@ -1347,77 +1373,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>db292580-e8c9-40b6-881b-4a9c4812858f</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>5164f990-a382-4d27-b5ab-ea0741664240</t>
         </is>
@@ -1434,31 +1460,26 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1476,35 +1497,40 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>6bfca8d7-d480-46e8-886a-9ceb5e93931d</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>8e7c4095-e059-43a9-901b-03edddc88181</t>
         </is>
@@ -1521,77 +1547,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>770e9930-60ee-4346-9462-a30c70a7a01d</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>090a6877-f7c0-4740-8e1e-9e7ec1b40f2e</t>
         </is>
@@ -1608,31 +1634,26 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1650,35 +1671,40 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>feb3a903-390f-4e40-bbaa-5e514b84f2ee</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>2323bc5d-ffdf-498e-a1e4-973fbdb0064d</t>
         </is>
@@ -1695,77 +1721,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>74068ed4-9266-4b5b-8826-1c88647c909b</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>4fe8181c-355a-4bb5-9a37-2fe962345f46</t>
         </is>
@@ -1782,31 +1808,26 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1824,35 +1845,40 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>d37cccf9-70ef-4340-9068-95356c48b69f</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>9cbd364d-a8a0-4b8d-b984-4d19cb73c231</t>
         </is>
@@ -1869,77 +1895,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>f8f7385e-1c46-4d37-a332-9bd8b06eda55</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>c25c678f-43a0-42a4-ba44-48e2a937b21c</t>
         </is>
@@ -1956,77 +1982,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>e2c3679d-db68-47b7-851a-56f91ecf737c</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>cdd4cb4f-cec2-436b-97db-97ab11792b46</t>
         </is>
@@ -2043,77 +2069,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>7f9a0958-eac3-491c-b4a1-4d458b951eda</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>d9d1c168-e7d5-4230-83e6-e138556c42d2</t>
         </is>
@@ -2130,77 +2156,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>7560e9ac-fd69-48f4-89ef-945f97aeb9e3</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>cdb0c1fc-b9cc-42f3-97cb-58f6ecdbe994</t>
         </is>
@@ -2217,77 +2243,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>e05af597-f2cc-4265-ba53-2d76f3523177</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>9cf63bc6-747b-49ce-bd55-bb1047c42b23</t>
         </is>
@@ -2304,77 +2330,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>8ee7381e-3ed1-4570-aa37-d4be2a70cb72</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>7047b8a8-5e9d-4a20-a7b9-c3d0eca6dd38</t>
         </is>
@@ -2391,77 +2417,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>03e77b21-561c-46fd-8a05-3ee266a73b61</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>782bb8bb-4884-4ee5-b65d-4a5ee5f843d2</t>
         </is>
@@ -2478,77 +2504,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>2f3e9923-de59-440e-bf17-b4cc497ea2bf</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>7ae4bef8-6bdf-45d9-b9a0-cafd0212174d</t>
         </is>
@@ -2565,77 +2591,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>9334ea8b-f2d9-496a-8f72-023457539125</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>ebb35e55-0384-47b8-b978-7c7e5f3c522f</t>
         </is>
@@ -2652,31 +2678,26 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>KD</t>
@@ -2694,35 +2715,40 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>075fe23a-8460-4672-a7ca-acd30910b3cb</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>28cfc718-2b35-4180-a106-860a48dc8046</t>
         </is>
@@ -2739,77 +2765,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>784e6497-b1af-4753-93ad-b106b6d0c844</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>c6c485d9-864d-4962-9271-bbfed309ec20</t>
         </is>
@@ -2826,77 +2852,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>7e770415-d67d-450b-ad89-4ca178ff8048</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>35219489-4c87-40d3-83d7-776176052337</t>
         </is>
@@ -2913,77 +2939,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>133033d4-8d81-4513-8bc9-b6c5e77fe612</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>7fff9064-d1ea-4aa7-83a0-96c74924aace</t>
         </is>
@@ -3000,77 +3026,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>3e4a2047-c77e-4b74-884a-04a314b235aa</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>069c6d48-5a68-44c0-bcac-73f1156b6bd6</t>
         </is>
@@ -3087,77 +3113,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>0027ee42-d7bc-49fd-9e78-a46ae1b398f1</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>05df27ab-520a-4518-aa8c-fa80da0a3850</t>
         </is>
@@ -3174,77 +3200,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>ba7bf275-a5b0-42bc-b1ec-be1ad7fbc75a</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>64f043b1-fa88-4bbd-b7b5-2debeedd81d9</t>
         </is>
@@ -3281,125 +3307,130 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="I38" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="K38" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K38" s="1" t="inlineStr">
+      <c r="L38" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L38" s="1" t="inlineStr">
+      <c r="M38" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M38" s="1" t="inlineStr">
+      <c r="N38" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N38" s="1" t="inlineStr">
+      <c r="O38" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O38" s="1" t="inlineStr">
+      <c r="P38" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P38" s="1" t="inlineStr">
+      <c r="Q38" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q38" s="1" t="inlineStr">
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R38" s="1" t="inlineStr">
+      <c r="S38" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S38" s="1" t="inlineStr">
+      <c r="T38" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T38" s="1" t="inlineStr">
+      <c r="U38" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U38" s="1" t="inlineStr">
+      <c r="V38" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V38" s="1" t="inlineStr">
+      <c r="W38" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W38" s="1" t="inlineStr">
+      <c r="X38" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X38" s="1" t="inlineStr">
+      <c r="Y38" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z38" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA38" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB38" s="1" t="inlineStr">
+      <c r="AC38" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC38" s="1" t="inlineStr">
+      <c r="AD38" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3416,47 +3447,47 @@
           <t>1 &lt;2</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>4010c4de-ca7d-43b5-80c2-39420f322390</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>c2145da6-8133-43e7-82e9-d526d1e8e008</t>
         </is>
@@ -3473,87 +3504,87 @@
           <t>1 &lt;2 ,2</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>-5 -6 -8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>-5 -6 -8</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+3 +3 +1</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+3 +3 +1</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+6 +3 +1</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>+6 +3 +1</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>5,15,18</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>5,15,18</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>ea51b9dc-ec41-4844-915f-fcc2e0182211</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>4e783e8b-8f73-4b6a-ab92-73dffae1289e</t>
         </is>
@@ -3570,87 +3601,87 @@
           <t>df+1 ,2</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Double Face Buster</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Double Face Buster</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>-3 -6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>-3 -6</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+8 +5</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+8 +5</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+8 +5</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>+8 +5</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>16,10</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>16,10</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>441d92ac-a0d1-4705-94ce-e357656c56a6</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>55b23cd6-5bdb-4c04-935f-140c039ac989</t>
         </is>
@@ -3667,87 +3698,87 @@
           <t>1 ,1 &lt;2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-5 -6 -14</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-5 -6 -14</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>+3 +2 KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>+3 +2 KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>+6 +2 KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>+6 +2 KD</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>5,8,15</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>5,8,15</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>7ab169f8-adb0-4b25-8cfc-03b3cc4bd33c</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>4afc7664-7977-441d-81a0-7fb8aa9d507b</t>
         </is>
@@ -3764,41 +3795,36 @@
           <t>D,f+1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Cat Thrust</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Cat Thrust</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3816,40 +3842,45 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>226e93a5-c8d6-40d4-baa0-2d0427ff0e29</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>11daf819-ca80-435d-9267-096646279402</t>
         </is>
@@ -3866,41 +3897,36 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Lunging Double Fist</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Lunging Double Fist</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3918,35 +3944,40 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>d3dfff3c-deee-466d-95aa-215d3dfc7ef8</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>c8eddceb-b485-4e14-9b2d-6bb641f12796</t>
         </is>
@@ -3963,41 +3994,36 @@
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Black Shoulder</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Black Shoulder</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4015,40 +4041,45 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>cbf7086b-a415-49f3-8ead-9dafa8bf2f9d</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>0fd990a5-b8ac-450d-84cc-073e0cfa8e7c</t>
         </is>
@@ -4065,41 +4096,36 @@
           <t>uf+1+2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Knuckle Bomb</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Knuckle Bomb</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4117,35 +4143,40 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>1550568d-fe8a-4ade-ab25-627330533c53</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>174e049e-f775-4037-862c-44fe5bb4ca01</t>
         </is>
@@ -4162,41 +4193,36 @@
           <t>uf,N+1+2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Jumping Knuckle Bomb</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Jumping Knuckle Bomb</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4214,35 +4240,40 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>476e9224-f981-40d5-8a16-c3f0547ff790</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>7396b42a-4d66-4761-86c7-0b904303e5c7</t>
         </is>
@@ -4259,87 +4290,87 @@
           <t>2 ,2</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-2 -13</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-2 -13</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>f1ffcd92-dfee-4028-a67d-d8d5aad4d106</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>4ac1d260-ce4f-449b-9eb9-1f4e6708d3af</t>
         </is>
@@ -4356,41 +4387,36 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Demon Gut Punch</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Demon Gut Punch</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4408,40 +4434,45 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>a5a621fd-1dc0-491b-9ab2-f256225083d0</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>e5feaca3-846a-43f3-98bf-5242eb391187</t>
         </is>
@@ -4458,41 +4489,36 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Front Strike</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Front Strike</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4510,35 +4536,40 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>22d07985-ed80-4087-b7ed-09625bb4da97</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>a472664b-a6d2-41e2-b2ff-4b7010db3559</t>
         </is>
@@ -4555,92 +4586,92 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>JGc SH</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>19ca8c2b-e184-4a81-9d51-dba1092ae4a1</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>364c42f0-d9cb-4a1a-8bd7-bbe23f97ff9c</t>
         </is>
@@ -4657,51 +4688,46 @@
           <t>D,f+2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Scarlett Windmill</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Scarlett Windmill</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-26</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-26</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4709,40 +4735,45 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>ca26431b-9945-49f2-ae0f-a0e3d26436bf</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>1bde543a-ea90-4f3b-a51c-a6996f95d595</t>
         </is>
@@ -4759,41 +4790,36 @@
           <t>D,df+2</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Scarlet Sweep</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Scarlet Sweep</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4811,40 +4837,45 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>ebb8cfaf-a5e0-45dd-b625-7185d31aa037</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>e66a6406-a2d8-430f-b208-d62923a0568b</t>
         </is>
@@ -4861,41 +4892,36 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4913,35 +4939,40 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>56637048-718b-4dfd-9c98-110a0a1a3def</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>e30e19ea-d6d1-4515-aa5d-e7f2fa7a76bd</t>
         </is>
@@ -4958,41 +4989,36 @@
           <t>ub+3</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Back Flip Kick</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Back Flip Kick</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-22</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-22</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5010,35 +5036,40 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>a99f5324-eced-445e-8ebd-9ae0ceb6d09e</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>c7fb74a1-53c9-4857-901e-e3fab3927d73</t>
         </is>
@@ -5055,97 +5086,97 @@
           <t>ub+3 ,2</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>– Tooth Fairy</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Back Flip Kick – Tooth Fairy</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-22 -18</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O56" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>20,25</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>71160db6-3d56-4706-a9f9-256c56cd233d</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>fc995e7a-5b07-4727-bbeb-0193756e4689</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>a99f5324-eced-445e-8ebd-9ae0ceb6d09e</t>
         </is>
@@ -5162,97 +5193,97 @@
           <t>uf+3 ,4 ,3</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Hunting Hawk</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Hunting Hawk</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>27 x x</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>27 x x</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-6 +7 x</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-6 +7 x</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>15,14,25</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>15,14,25</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>If the 1st hit is blocked the 3rd hit is cancelled. If the first hit whiffs the string ends.</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>883932e4-1d0d-4431-8f45-242de9a6d6f7</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>98fd3ae9-e310-45dd-9d74-96b4ba2dd978</t>
         </is>
@@ -5269,92 +5300,92 @@
           <t>FC+3 ,3 ,d+3</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Snake Creep</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Snake Creep</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-14 -19 -17</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-14 -19 -17</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>-3 -9 -3</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>-3 -9 -3</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>-3 -9 -3</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>-3 -9 -3</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>12,19,7</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>12,19,7</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>33cfe2bb-c500-4640-8cab-fa812aa44fad</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>e36a327a-f820-47ad-96d1-a960af7de3d7</t>
         </is>
@@ -5371,97 +5402,97 @@
           <t>FC+3 ,3 ,N+3</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Snake Blade</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Snake Blade</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-14 -19 -15</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-14 -19 -15</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>-3 -9 KD</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>-3 -9 KD</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>-3 -9 KD</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>-3 -9 KD</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>12,19,25</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>12,19,25</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>LLm</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>LLm</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>ee4c4b9f-45fd-4f23-96ee-8df9e8e595c2</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>9daa4cf3-facd-467d-81bd-10f45d35330d</t>
         </is>
@@ -5478,87 +5509,87 @@
           <t>WS+3 ,3</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-19 -19</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-19 -19</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>-8 -8</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>-8 -8</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>-8 -8</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>-8 -8</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>2b56e266-f24a-4c2b-8e84-4da5456bffaf</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>a8b0b1fe-302b-4efc-afbb-542e10a5e9eb</t>
         </is>
@@ -5575,92 +5606,92 @@
           <t>WS+3 ,3 ,df+3</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>– Step In Kick Infinite Starter</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Tsunami Kick – Step In Kick Infinite Starter</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-19 -19 -14</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>-8 -8 -3</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>-8 -8 -3</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>10,25,15</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>The Infinite Kicks have to be started with 1 Silver Low or 1 Step In Kick after the WS+3,3.</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>fa27a5fa-d864-4152-b24d-58d5722b728d</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>555cfacb-bc27-4098-a8f6-4633d88ead26</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>2b56e266-f24a-4c2b-8e84-4da5456bffaf</t>
         </is>
@@ -5677,92 +5708,92 @@
           <t>WS+3 ,3 ,D+3</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>– Silver Low Infinite Starter</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Tsunami Kick – Silver Low Infinite Starter</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-19 -19 -19</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>-8 -8 -8</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>-8 -8 -8</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>10,25,15</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>mml</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>The Infinite Kicks have to be started with 1 Silver Low or 1 Step In Kick after the WS+3,3.</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>7809ddfe-2eea-46d3-bbe9-bec01c1df11e</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>7536fcaa-0cdb-48a0-aaa5-5c9640d8f9a7</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>2b56e266-f24a-4c2b-8e84-4da5456bffaf</t>
         </is>
@@ -5779,92 +5810,92 @@
           <t>WS+3 ,3 ,D+3 ,3 ,3 ,3 ,3...</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>–– Rave Kicks</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-19 -16 -19 -16...</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-19 -19 -19 -19 -16 -19 -16...</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>-8 -5 -8 -5...</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5...</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>-8 -5 -8 -5...</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5...</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>10,10,10,10...</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>10,10,10,10...</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>10,25,15,10,10,10,10...</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>mhmh</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>mmlmhmh</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Sequence of the Infinite is 2 Rave Kicks, Feint Hammer or Low Silver, 2 Rave Kicks, Feint Hammer or Silver Low...</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>60fa1290-a9ab-4683-9495-25402b0c33b2</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>5cb61a54-0717-49e9-9f6d-3de69c2a9c9c</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>7809ddfe-2eea-46d3-bbe9-bec01c1df11e</t>
         </is>
@@ -5881,92 +5912,92 @@
           <t>WS+3 ,3 ,D+3 ,3 ,3 ,3 ,3... ,u+3 ,3 ,3...</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>––– Feint Hammer - Rave Kicks</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks – Feint Hammer - Rave Kicks</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-19 -16 -19...</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-19 -19 -19 -19 -16 -19 -16... -19 -16 -19...</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>-8 -5 -8...</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>-8 -5 -8...</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>15,10,10...</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>15,10,10...</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>10,25,15,10,10,10,10...,15,10,10...</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>mmlmhmhmmh</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Sequence of the Infinite is 2 Rave Kicks, Feint Hammer or Low Silver, 2 Rave Kicks, Feint Hammer or Silver Low...</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>c399272a-956c-442c-b7fe-1e06200547a9</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>43752b7b-1866-4b30-92ed-5decf175f64d</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>60fa1290-a9ab-4683-9495-25402b0c33b2</t>
         </is>
@@ -5983,92 +6014,92 @@
           <t>WS+3 ,3 ,D+3 ,3 ,3 ,3 ,3... ,d+3 ,3 ,3...</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>––– Silver Low - Rave Kicks</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks – Silver Low - Rave Kicks</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-19 -16 -19...</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-19 -19 -19 -19 -16 -19 -16... -19 -16 -19...</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>-8 -5 -8...</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>-8 -5 -8...</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>15,10,10...</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>15,10,10...</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>10,25,15,10,10,10,10...,15,10,10...</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>lmh</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>mmlmhmhlmh</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Sequence of the Infinite is 2 Rave Kicks, Feint Hammer or Low Silver, 2 Rave Kicks, Feint Hammer or Silver Low...</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>d0e95208-5cae-49e6-8686-366146a5264c</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>8a5bd9dc-2179-4c0b-80f1-c266fd4a79a8</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>60fa1290-a9ab-4683-9495-25402b0c33b2</t>
         </is>
@@ -6085,31 +6116,26 @@
           <t>f,f+3+4</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Exploder</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Exploder</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6127,40 +6153,45 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>632f10d4-5d08-4bc1-a7d1-0b85b14114ad</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>88a49497-4c99-4054-8745-87037895d876</t>
         </is>
@@ -6177,31 +6208,26 @@
           <t>f,f,N+3+4</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Delayed Dragon Slide</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Delayed Dragon Slide</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6219,35 +6245,40 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>7507033e-5d61-4d3d-abe2-7c384d3e74d3</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>3fd1d311-a9f4-4f7b-b899-05ba6aeace9f</t>
         </is>
@@ -6264,41 +6295,36 @@
           <t>WS+3+4</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Spin Kick</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Spin Kick</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6316,35 +6342,40 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>c125db06-23f3-4b2b-be27-7b4bba3890dc</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>f2211d59-4927-4700-8ee4-e4886e68145f</t>
         </is>
@@ -6361,51 +6392,46 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Axe Kick</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Axe Kick</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>+11</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6413,40 +6439,45 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>KSco GB</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>82143dbe-e59b-4efc-9cc8-cff79241ab4d</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>e3cf0536-4246-46fe-97ed-4f8cfea02423</t>
         </is>
@@ -6463,41 +6494,36 @@
           <t>SS+4</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Azteca Shoot</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Azteca Shoot</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6515,40 +6541,45 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>7d1fb39f-1894-49ad-b23f-e5db89be13a1</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>fb1a0851-bbcc-4b80-bbbf-ef540491952e</t>
         </is>
@@ -6565,41 +6596,36 @@
           <t>d,db+4</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Blazing Kick</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Blazing Kick</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6617,45 +6643,50 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>5b005f64-6204-4b39-9062-df29a019045b</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>36f0eced-9509-425b-ac26-ff0dd509d675</t>
         </is>
@@ -6672,87 +6703,87 @@
           <t>d+4 ,4</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Laser Edge - Machine Gun Kick</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Laser Edge - Machine Gun Kick</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-11 -9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-11 -9</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>-12 0</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>-12 0</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>7,20</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>7,20</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>lh</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>lh</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>9318193d-c16a-4d81-b608-749fd82f3894</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>2ea85a0a-da3a-4b9f-8403-16f46dfec807</t>
         </is>
@@ -6769,41 +6800,36 @@
           <t>f,f+4</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Bazooka Kick</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Bazooka Kick</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6821,40 +6847,45 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>a9fdd58b-6916-4c51-8c9a-47da5702d9dd</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>05788a5e-e33a-4251-8d15-05d315c66167</t>
         </is>
@@ -6871,41 +6902,36 @@
           <t>f,f,N+4</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Hammer Heel</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Hammer Heel</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6923,35 +6949,40 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>77bab312-bab4-4bbf-8f52-1285ee89ec03</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>efcfe32d-0f73-41bd-b995-d12ff6088c86</t>
         </is>
@@ -6968,87 +6999,87 @@
           <t>WS+4 ,4</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-3 -15</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>-3 -15</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>13,18</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>13,18</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>f8e6172e-52f2-46bc-a653-0554694b03cd</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>dfab5a90-083f-4b80-a10e-cfbf86c10c3a</t>
         </is>
@@ -7065,31 +7096,26 @@
           <t>4 ~3</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Scissors Kick</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Scissors Kick</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7107,35 +7133,40 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>0c226639-691e-4f16-abdd-e7a77c2f1850</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>4533fac1-24a2-4832-9359-461ebe671a74</t>
         </is>
@@ -7152,52 +7183,52 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Ancient Power</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Ancient Power</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>High Attack reversal.</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>1b5b4651-7b1d-455b-b965-9af0194d12ba</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>c570243b-71ad-40da-9056-c34db3d1ec64</t>
         </is>
@@ -7234,125 +7265,130 @@
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
+      <c r="H80" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
+      <c r="I80" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I80" s="1" t="inlineStr">
+      <c r="J80" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
+      <c r="K80" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K80" s="1" t="inlineStr">
+      <c r="L80" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
+      <c r="M80" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
+      <c r="N80" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
+      <c r="O80" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
+      <c r="P80" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P80" s="1" t="inlineStr">
+      <c r="Q80" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q80" s="1" t="inlineStr">
+      <c r="R80" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R80" s="1" t="inlineStr">
+      <c r="S80" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S80" s="1" t="inlineStr">
+      <c r="T80" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T80" s="1" t="inlineStr">
+      <c r="U80" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U80" s="1" t="inlineStr">
+      <c r="V80" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V80" s="1" t="inlineStr">
+      <c r="W80" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W80" s="1" t="inlineStr">
+      <c r="X80" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X80" s="1" t="inlineStr">
+      <c r="Y80" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y80" s="1" t="inlineStr">
+      <c r="Z80" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z80" s="1" t="inlineStr">
+      <c r="AA80" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA80" s="1" t="inlineStr">
+      <c r="AB80" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB80" s="1" t="inlineStr">
+      <c r="AC80" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC80" s="1" t="inlineStr">
+      <c r="AD80" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7369,31 +7405,26 @@
           <t>db+1+2</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Bloody Scissors</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Bloody Scissors</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7411,35 +7442,40 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>b75d5edf-c657-4292-95f8-05b8676aad1b</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>5ec6acd4-ae8b-4475-8592-6d71272b1900</t>
         </is>
@@ -7463,29 +7499,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>uf+1+2~D</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7503,35 +7539,40 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>eebf31c0-8967-42b2-bdd1-eb952a3753b7</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>92e7265a-ffb0-4a60-a758-f4aecbf93eb9</t>
         </is>
@@ -7555,29 +7596,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>uf,N+1+2~D</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Jump In Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Jump In Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7595,35 +7636,40 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>68a6c808-f0d7-46e6-882f-3beab2146722</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>90488c55-5438-43eb-8a27-e1ab4b605976</t>
         </is>
@@ -7640,31 +7686,26 @@
           <t>b,b+1+2</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Indigo Punch</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Indigo Punch</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7682,35 +7723,40 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>42089346-2e0b-4290-bf0f-0bd5d03d04da</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>75d14b22-f966-4fdf-9c87-dbfbb074bda3</t>
         </is>
@@ -7727,31 +7773,26 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Deadly Spear</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Deadly Spear</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7769,45 +7810,50 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
           <t>15,20</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>15,20</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>CFS</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>After blocking the 1st hit, the unblockable hit can be avoided by a SS or Back Dash.</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>86004fb4-2351-43cf-8e99-15d6ecf057fb</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>069c6ba7-3cae-4a09-931d-73c171287938</t>
         </is>
@@ -7824,31 +7870,26 @@
           <t>b+2</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Kunai Stab</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Kunai Stab</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7866,35 +7907,40 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>ad5b5270-34ef-42c7-afbb-48e39c22af0e</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>27edfdc7-e025-4885-bb89-5be8d0da580b</t>
         </is>
@@ -7911,31 +7957,26 @@
           <t>f,f,N+2</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Kunai Advance</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Kunai Advance</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7953,35 +7994,40 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>e129dd87-4b11-4f24-818a-f631af159c26</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>a419541d-83de-483a-9a68-14844e9eddca</t>
         </is>
@@ -7998,31 +8044,26 @@
           <t>b+2+3</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Sidewinder</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Sidewinder</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8040,35 +8081,40 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>de330659-ea98-473c-adac-de05566184f9</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>f21b2047-ec49-4179-8017-1184fb542bec</t>
         </is>
@@ -8105,125 +8151,130 @@
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F91" s="1" t="inlineStr">
+      <c r="G91" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr">
+      <c r="H91" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H91" s="1" t="inlineStr">
+      <c r="I91" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I91" s="1" t="inlineStr">
+      <c r="J91" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J91" s="1" t="inlineStr">
+      <c r="K91" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K91" s="1" t="inlineStr">
+      <c r="L91" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L91" s="1" t="inlineStr">
+      <c r="M91" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M91" s="1" t="inlineStr">
+      <c r="N91" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N91" s="1" t="inlineStr">
+      <c r="O91" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O91" s="1" t="inlineStr">
+      <c r="P91" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P91" s="1" t="inlineStr">
+      <c r="Q91" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q91" s="1" t="inlineStr">
+      <c r="R91" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R91" s="1" t="inlineStr">
+      <c r="S91" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S91" s="1" t="inlineStr">
+      <c r="T91" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T91" s="1" t="inlineStr">
+      <c r="U91" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U91" s="1" t="inlineStr">
+      <c r="V91" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V91" s="1" t="inlineStr">
+      <c r="W91" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W91" s="1" t="inlineStr">
+      <c r="X91" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X91" s="1" t="inlineStr">
+      <c r="Y91" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y91" s="1" t="inlineStr">
+      <c r="Z91" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z91" s="1" t="inlineStr">
+      <c r="AA91" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA91" s="1" t="inlineStr">
+      <c r="AB91" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB91" s="1" t="inlineStr">
+      <c r="AC91" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC91" s="1" t="inlineStr">
+      <c r="AD91" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
